--- a/output/mumps_latex.xlsx
+++ b/output/mumps_latex.xlsx
@@ -453,16 +453,16 @@
         <v>0.2695</v>
       </c>
       <c r="C2" t="n">
-        <v>155</v>
+        <v>78</v>
       </c>
       <c r="D2" t="n">
-        <v>4706</v>
+        <v>1870</v>
       </c>
       <c r="E2" t="n">
-        <v>646</v>
+        <v>298</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -473,16 +473,16 @@
         <v>0.2154</v>
       </c>
       <c r="C3" t="n">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="D3" t="n">
-        <v>2215</v>
+        <v>1788</v>
       </c>
       <c r="E3" t="n">
-        <v>393</v>
+        <v>356</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -493,16 +493,16 @@
         <v>0.1559</v>
       </c>
       <c r="C4" t="n">
-        <v>144</v>
+        <v>55</v>
       </c>
       <c r="D4" t="n">
-        <v>1769</v>
+        <v>1122</v>
       </c>
       <c r="E4" t="n">
-        <v>420</v>
+        <v>179</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -513,13 +513,13 @@
         <v>0.08914999999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>128</v>
+        <v>66</v>
       </c>
       <c r="D5" t="n">
-        <v>1174</v>
+        <v>507</v>
       </c>
       <c r="E5" t="n">
-        <v>337</v>
+        <v>153</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -533,16 +533,16 @@
         <v>0.01351</v>
       </c>
       <c r="C6" t="n">
-        <v>384</v>
+        <v>54</v>
       </c>
       <c r="D6" t="n">
-        <v>1678</v>
+        <v>321</v>
       </c>
       <c r="E6" t="n">
-        <v>769</v>
+        <v>109</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -553,16 +553,16 @@
         <v>0.008151</v>
       </c>
       <c r="C7" t="n">
-        <v>251</v>
+        <v>57</v>
       </c>
       <c r="D7" t="n">
-        <v>1132</v>
+        <v>308</v>
       </c>
       <c r="E7" t="n">
-        <v>503</v>
+        <v>118</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -573,16 +573,16 @@
         <v>0.006007</v>
       </c>
       <c r="C8" t="n">
-        <v>235</v>
+        <v>68</v>
       </c>
       <c r="D8" t="n">
-        <v>1130</v>
+        <v>366</v>
       </c>
       <c r="E8" t="n">
-        <v>477</v>
+        <v>138</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -593,16 +593,16 @@
         <v>0.005191</v>
       </c>
       <c r="C9" t="n">
-        <v>189</v>
+        <v>21</v>
       </c>
       <c r="D9" t="n">
-        <v>1403</v>
+        <v>117</v>
       </c>
       <c r="E9" t="n">
-        <v>443</v>
+        <v>40</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -610,19 +610,19 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.003212</v>
+        <v>0.003211</v>
       </c>
       <c r="C10" t="n">
-        <v>418</v>
+        <v>96</v>
       </c>
       <c r="D10" t="n">
-        <v>2698</v>
+        <v>852</v>
       </c>
       <c r="E10" t="n">
-        <v>908</v>
+        <v>234</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -630,19 +630,19 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.002446</v>
+        <v>0.002447</v>
       </c>
       <c r="C11" t="n">
-        <v>1108</v>
+        <v>70</v>
       </c>
       <c r="D11" t="n">
-        <v>10616</v>
+        <v>568</v>
       </c>
       <c r="E11" t="n">
-        <v>2915</v>
+        <v>173</v>
       </c>
       <c r="F11" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -650,19 +650,19 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.00203</v>
+        <v>0.002621</v>
       </c>
       <c r="C12" t="n">
-        <v>1841</v>
+        <v>37</v>
       </c>
       <c r="D12" t="n">
-        <v>14298</v>
+        <v>213</v>
       </c>
       <c r="E12" t="n">
-        <v>4420</v>
+        <v>141</v>
       </c>
       <c r="F12" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
